--- a/data/Internal_Investments_Dashboard.xlsx
+++ b/data/Internal_Investments_Dashboard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/internal-models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/market-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F212B6ED-62DC-CD46-993B-410DDA69539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209639B8-407D-4946-909A-1682B75F95FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3460" yWindow="2660" windowWidth="27640" windowHeight="16680" xr2:uid="{FBFB69EE-18FE-594B-9D4F-6699E2689A0B}"/>
+    <workbookView xWindow="40060" yWindow="1740" windowWidth="27640" windowHeight="16680" xr2:uid="{FBFB69EE-18FE-594B-9D4F-6699E2689A0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments Map Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="59">
   <si>
     <t>Partner</t>
   </si>
@@ -92,9 +92,6 @@
     <t>South-East Asia</t>
   </si>
   <si>
-    <t>India</t>
-  </si>
-  <si>
     <t>Private Equity</t>
   </si>
   <si>
@@ -113,18 +110,12 @@
     <t>Europe</t>
   </si>
   <si>
-    <t xml:space="preserve"> Later-Stage</t>
-  </si>
-  <si>
     <t>Broad</t>
   </si>
   <si>
     <t>Apollo Private Equity</t>
   </si>
   <si>
-    <t>Asia-Pacific</t>
-  </si>
-  <si>
     <t>Lone Star</t>
   </si>
   <si>
@@ -152,12 +143,6 @@
     <t>Tiger Global Private Investment Partners</t>
   </si>
   <si>
-    <t>Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Growth</t>
-  </si>
-  <si>
     <t>Tiger Global Crossover</t>
   </si>
   <si>
@@ -167,9 +152,6 @@
     <t>Seed</t>
   </si>
   <si>
-    <t xml:space="preserve"> Early-Stage</t>
-  </si>
-  <si>
     <t>Intellectual Property</t>
   </si>
   <si>
@@ -188,9 +170,6 @@
     <t>B2B SaaS</t>
   </si>
   <si>
-    <t xml:space="preserve"> fintech</t>
-  </si>
-  <si>
     <t>Incus Capital</t>
   </si>
   <si>
@@ -200,15 +179,6 @@
     <t>Renewables</t>
   </si>
   <si>
-    <t xml:space="preserve"> Energy transition</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> essential services</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> public transport</t>
-  </si>
-  <si>
     <t>Grovepoint</t>
   </si>
   <si>
@@ -224,7 +194,25 @@
     <t xml:space="preserve">Private Equity </t>
   </si>
   <si>
-    <t xml:space="preserve"> Mature</t>
+    <t>South Asia</t>
+  </si>
+  <si>
+    <t>Later-Stage</t>
+  </si>
+  <si>
+    <t>East Asia</t>
+  </si>
+  <si>
+    <t>Fintech</t>
+  </si>
+  <si>
+    <t>Energy transition</t>
+  </si>
+  <si>
+    <t>Essential services</t>
+  </si>
+  <si>
+    <t>Public transport</t>
   </si>
 </sst>
 </file>
@@ -233,9 +221,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -259,21 +247,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -292,12 +269,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor theme="7" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -348,31 +325,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF4472C4"/>
+        <color theme="7"/>
       </left>
       <right style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </right>
       <top style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB4C6E7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB4C6E7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB4C6E7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB4C6E7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -381,7 +343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -392,46 +354,27 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -765,17 +708,37 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{CA538ADB-FD1C-AA45-8227-90AD9354DCA5}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD116F1-5EB1-BC40-9EB8-BFB75BCF5702}">
   <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="4" width="19" style="16" customWidth="1"/>
-    <col min="5" max="6" width="30" style="17" customWidth="1"/>
-    <col min="7" max="9" width="39.1640625" style="16" customWidth="1"/>
-    <col min="10" max="12" width="23.5" style="16" customWidth="1"/>
-    <col min="13" max="13" width="36" style="16" customWidth="1"/>
+    <col min="2" max="4" width="19" style="5" customWidth="1"/>
+    <col min="5" max="6" width="30" style="6" customWidth="1"/>
+    <col min="7" max="9" width="39.1640625" style="5" customWidth="1"/>
+    <col min="10" max="12" width="23.5" style="5" customWidth="1"/>
+    <col min="13" max="13" width="36" style="5" customWidth="1"/>
     <col min="14" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -829,563 +792,557 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9">
+        <v>50000000</v>
+      </c>
+      <c r="F2" s="9">
+        <v>1000000000</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6">
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="12">
+        <v>100000000</v>
+      </c>
+      <c r="F3" s="12">
+        <v>1000000000</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9">
+        <v>1000000000</v>
+      </c>
+      <c r="F4" s="9">
+        <v>10000000000</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="12">
+        <v>500000000</v>
+      </c>
+      <c r="F5" s="12">
+        <v>5000000000</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="9">
+        <v>10000000</v>
+      </c>
+      <c r="F6" s="9">
+        <v>100000000</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="F7" s="12">
         <v>50000000</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9">
+        <v>50000000</v>
+      </c>
+      <c r="F8" s="9">
+        <v>500000000</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="12">
         <v>1000000000</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F9" s="12">
+        <v>500000000000</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5" t="s">
+      <c r="K9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+    </row>
+    <row r="10" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="F10" s="9">
+        <v>50000000</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="F11" s="12">
+        <v>100000000</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="F12" s="9">
+        <v>10000000</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="F13" s="12">
+        <v>100000000</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="F14" s="9">
+        <v>25000000</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10">
-        <v>100000000</v>
-      </c>
-      <c r="F3" s="10">
-        <v>1000000000</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="9">
+        <v>5000000</v>
+      </c>
+      <c r="F16" s="9">
+        <v>25000000</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-    </row>
-    <row r="4" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="K16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="11">
-        <v>1000000000</v>
-      </c>
-      <c r="F4" s="11">
-        <v>10000000000</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="13">
-        <v>500000000</v>
-      </c>
-      <c r="F5" s="13">
-        <v>5000000000</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-    </row>
-    <row r="6" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="6">
-        <v>10000000</v>
-      </c>
-      <c r="F6" s="6">
-        <v>100000000</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-    </row>
-    <row r="7" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10">
-        <v>10000000</v>
-      </c>
-      <c r="F7" s="10">
-        <v>50000000</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-    </row>
-    <row r="8" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6">
-        <v>50000000</v>
-      </c>
-      <c r="F8" s="6">
-        <v>500000000</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-    </row>
-    <row r="9" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10">
-        <v>1000000000</v>
-      </c>
-      <c r="F9" s="10">
-        <v>500000000000</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-    </row>
-    <row r="10" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="11">
-        <v>1000000</v>
-      </c>
-      <c r="F10" s="11">
-        <v>50000000</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-    </row>
-    <row r="11" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10">
-        <v>10000000</v>
-      </c>
-      <c r="F11" s="10">
-        <v>100000000</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-    </row>
-    <row r="12" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="11">
-        <v>1000000</v>
-      </c>
-      <c r="F12" s="11">
-        <v>10000000</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-    </row>
-    <row r="13" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="13">
-        <v>10000000</v>
-      </c>
-      <c r="F13" s="13">
-        <v>100000000</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6">
-        <v>1000000</v>
-      </c>
-      <c r="F14" s="6">
-        <v>25000000</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-    </row>
-    <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-    </row>
-    <row r="16" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6">
-        <v>5000000</v>
-      </c>
-      <c r="F16" s="6">
-        <v>25000000</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
     </row>
     <row r="17" ht="35" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>

--- a/data/Internal_Investments_Dashboard.xlsx
+++ b/data/Internal_Investments_Dashboard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/market-dashboard/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/internal-models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209639B8-407D-4946-909A-1682B75F95FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F212B6ED-62DC-CD46-993B-410DDA69539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40060" yWindow="1740" windowWidth="27640" windowHeight="16680" xr2:uid="{FBFB69EE-18FE-594B-9D4F-6699E2689A0B}"/>
+    <workbookView xWindow="3460" yWindow="2660" windowWidth="27640" windowHeight="16680" xr2:uid="{FBFB69EE-18FE-594B-9D4F-6699E2689A0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments Map Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
   <si>
     <t>Partner</t>
   </si>
@@ -92,6 +92,9 @@
     <t>South-East Asia</t>
   </si>
   <si>
+    <t>India</t>
+  </si>
+  <si>
     <t>Private Equity</t>
   </si>
   <si>
@@ -110,12 +113,18 @@
     <t>Europe</t>
   </si>
   <si>
+    <t xml:space="preserve"> Later-Stage</t>
+  </si>
+  <si>
     <t>Broad</t>
   </si>
   <si>
     <t>Apollo Private Equity</t>
   </si>
   <si>
+    <t>Asia-Pacific</t>
+  </si>
+  <si>
     <t>Lone Star</t>
   </si>
   <si>
@@ -143,6 +152,12 @@
     <t>Tiger Global Private Investment Partners</t>
   </si>
   <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Growth</t>
+  </si>
+  <si>
     <t>Tiger Global Crossover</t>
   </si>
   <si>
@@ -152,6 +167,9 @@
     <t>Seed</t>
   </si>
   <si>
+    <t xml:space="preserve"> Early-Stage</t>
+  </si>
+  <si>
     <t>Intellectual Property</t>
   </si>
   <si>
@@ -170,6 +188,9 @@
     <t>B2B SaaS</t>
   </si>
   <si>
+    <t xml:space="preserve"> fintech</t>
+  </si>
+  <si>
     <t>Incus Capital</t>
   </si>
   <si>
@@ -179,6 +200,15 @@
     <t>Renewables</t>
   </si>
   <si>
+    <t xml:space="preserve"> Energy transition</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> essential services</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> public transport</t>
+  </si>
+  <si>
     <t>Grovepoint</t>
   </si>
   <si>
@@ -194,25 +224,7 @@
     <t xml:space="preserve">Private Equity </t>
   </si>
   <si>
-    <t>South Asia</t>
-  </si>
-  <si>
-    <t>Later-Stage</t>
-  </si>
-  <si>
-    <t>East Asia</t>
-  </si>
-  <si>
-    <t>Fintech</t>
-  </si>
-  <si>
-    <t>Energy transition</t>
-  </si>
-  <si>
-    <t>Essential services</t>
-  </si>
-  <si>
-    <t>Public transport</t>
+    <t xml:space="preserve"> Mature</t>
   </si>
 </sst>
 </file>
@@ -221,9 +233,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -247,10 +259,21 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -269,12 +292,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -325,16 +348,31 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="7"/>
+        <color rgb="FF4472C4"/>
       </left>
       <right style="thin">
-        <color theme="7"/>
+        <color rgb="FFB4C6E7"/>
       </right>
       <top style="thin">
-        <color theme="7"/>
+        <color rgb="FFB4C6E7"/>
       </top>
       <bottom style="thin">
-        <color theme="7"/>
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -343,7 +381,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -354,27 +392,46 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -708,37 +765,17 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{CA538ADB-FD1C-AA45-8227-90AD9354DCA5}">
-  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD116F1-5EB1-BC40-9EB8-BFB75BCF5702}">
   <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="4" width="19" style="5" customWidth="1"/>
-    <col min="5" max="6" width="30" style="6" customWidth="1"/>
-    <col min="7" max="9" width="39.1640625" style="5" customWidth="1"/>
-    <col min="10" max="12" width="23.5" style="5" customWidth="1"/>
-    <col min="13" max="13" width="36" style="5" customWidth="1"/>
+    <col min="2" max="4" width="19" style="16" customWidth="1"/>
+    <col min="5" max="6" width="30" style="17" customWidth="1"/>
+    <col min="7" max="9" width="39.1640625" style="16" customWidth="1"/>
+    <col min="10" max="12" width="23.5" style="16" customWidth="1"/>
+    <col min="13" max="13" width="36" style="16" customWidth="1"/>
     <col min="14" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -792,557 +829,563 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6">
+        <v>50000000</v>
+      </c>
+      <c r="F2" s="6">
+        <v>1000000000</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+    </row>
+    <row r="3" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="F3" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+    </row>
+    <row r="4" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="11">
+        <v>1000000000</v>
+      </c>
+      <c r="F4" s="11">
+        <v>10000000000</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+    </row>
+    <row r="5" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="13">
+        <v>500000000</v>
+      </c>
+      <c r="F5" s="13">
+        <v>5000000000</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+    </row>
+    <row r="6" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="6">
+        <v>10000000</v>
+      </c>
+      <c r="F6" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="10">
+        <v>10000000</v>
+      </c>
+      <c r="F7" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+    </row>
+    <row r="8" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6">
+        <v>50000000</v>
+      </c>
+      <c r="F8" s="6">
+        <v>500000000</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+    </row>
+    <row r="9" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="F9" s="10">
+        <v>500000000000</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+    </row>
+    <row r="10" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="F10" s="11">
+        <v>50000000</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+    </row>
+    <row r="11" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="10">
+        <v>10000000</v>
+      </c>
+      <c r="F11" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+    </row>
+    <row r="12" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="F12" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+    </row>
+    <row r="13" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="13">
+        <v>10000000</v>
+      </c>
+      <c r="F13" s="13">
+        <v>100000000</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9">
-        <v>50000000</v>
-      </c>
-      <c r="F2" s="9">
-        <v>1000000000</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8" t="s">
+      <c r="I13" s="14"/>
+      <c r="J13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="F14" s="6">
+        <v>25000000</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8" t="s">
+      <c r="H14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+    </row>
+    <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+    </row>
+    <row r="16" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6">
+        <v>5000000</v>
+      </c>
+      <c r="F16" s="6">
+        <v>25000000</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12">
-        <v>100000000</v>
-      </c>
-      <c r="F3" s="12">
-        <v>1000000000</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9">
-        <v>1000000000</v>
-      </c>
-      <c r="F4" s="9">
-        <v>10000000000</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="K16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="12">
-        <v>500000000</v>
-      </c>
-      <c r="F5" s="12">
-        <v>5000000000</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="9">
-        <v>10000000</v>
-      </c>
-      <c r="F6" s="9">
-        <v>100000000</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12">
-        <v>10000000</v>
-      </c>
-      <c r="F7" s="12">
-        <v>50000000</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9">
-        <v>50000000</v>
-      </c>
-      <c r="F8" s="9">
-        <v>500000000</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12">
-        <v>1000000000</v>
-      </c>
-      <c r="F9" s="12">
-        <v>500000000000</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9">
-        <v>1000000</v>
-      </c>
-      <c r="F10" s="9">
-        <v>50000000</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12">
-        <v>10000000</v>
-      </c>
-      <c r="F11" s="12">
-        <v>100000000</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9">
-        <v>1000000</v>
-      </c>
-      <c r="F12" s="9">
-        <v>10000000</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="12">
-        <v>10000000</v>
-      </c>
-      <c r="F13" s="12">
-        <v>100000000</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="P13" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9">
-        <v>1000000</v>
-      </c>
-      <c r="F14" s="9">
-        <v>25000000</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="9">
-        <v>5000000</v>
-      </c>
-      <c r="F16" s="9">
-        <v>25000000</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8" t="s">
-        <v>40</v>
-      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
     </row>
     <row r="17" ht="35" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>

--- a/data/Internal_Investments_Dashboard.xlsx
+++ b/data/Internal_Investments_Dashboard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/internal-models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/market-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F212B6ED-62DC-CD46-993B-410DDA69539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AA4812-AE04-5A4B-96BC-DD8676E64D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3460" yWindow="2660" windowWidth="27640" windowHeight="16680" xr2:uid="{FBFB69EE-18FE-594B-9D4F-6699E2689A0B}"/>
+    <workbookView xWindow="6560" yWindow="2480" windowWidth="27640" windowHeight="16680" xr2:uid="{FBFB69EE-18FE-594B-9D4F-6699E2689A0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments Map Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="59">
   <si>
     <t>Partner</t>
   </si>
@@ -92,9 +92,6 @@
     <t>South-East Asia</t>
   </si>
   <si>
-    <t>India</t>
-  </si>
-  <si>
     <t>Private Equity</t>
   </si>
   <si>
@@ -113,18 +110,12 @@
     <t>Europe</t>
   </si>
   <si>
-    <t xml:space="preserve"> Later-Stage</t>
-  </si>
-  <si>
     <t>Broad</t>
   </si>
   <si>
     <t>Apollo Private Equity</t>
   </si>
   <si>
-    <t>Asia-Pacific</t>
-  </si>
-  <si>
     <t>Lone Star</t>
   </si>
   <si>
@@ -152,12 +143,6 @@
     <t>Tiger Global Private Investment Partners</t>
   </si>
   <si>
-    <t>Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Growth</t>
-  </si>
-  <si>
     <t>Tiger Global Crossover</t>
   </si>
   <si>
@@ -167,9 +152,6 @@
     <t>Seed</t>
   </si>
   <si>
-    <t xml:space="preserve"> Early-Stage</t>
-  </si>
-  <si>
     <t>Intellectual Property</t>
   </si>
   <si>
@@ -188,9 +170,6 @@
     <t>B2B SaaS</t>
   </si>
   <si>
-    <t xml:space="preserve"> fintech</t>
-  </si>
-  <si>
     <t>Incus Capital</t>
   </si>
   <si>
@@ -200,15 +179,6 @@
     <t>Renewables</t>
   </si>
   <si>
-    <t xml:space="preserve"> Energy transition</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> essential services</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> public transport</t>
-  </si>
-  <si>
     <t>Grovepoint</t>
   </si>
   <si>
@@ -224,7 +194,25 @@
     <t xml:space="preserve">Private Equity </t>
   </si>
   <si>
-    <t xml:space="preserve"> Mature</t>
+    <t>South Asia</t>
+  </si>
+  <si>
+    <t>Later-Stage</t>
+  </si>
+  <si>
+    <t>East Asia</t>
+  </si>
+  <si>
+    <t>Fintech</t>
+  </si>
+  <si>
+    <t>Energy transition</t>
+  </si>
+  <si>
+    <t>Essential services</t>
+  </si>
+  <si>
+    <t>Public transport</t>
   </si>
 </sst>
 </file>
@@ -233,9 +221,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -259,21 +247,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -292,12 +269,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor theme="7" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -348,31 +325,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF4472C4"/>
+        <color theme="7"/>
       </left>
       <right style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </right>
       <top style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB4C6E7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB4C6E7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB4C6E7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB4C6E7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -381,7 +343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -392,46 +354,27 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -771,11 +714,11 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="4" width="19" style="16" customWidth="1"/>
-    <col min="5" max="6" width="30" style="17" customWidth="1"/>
-    <col min="7" max="9" width="39.1640625" style="16" customWidth="1"/>
-    <col min="10" max="12" width="23.5" style="16" customWidth="1"/>
-    <col min="13" max="13" width="36" style="16" customWidth="1"/>
+    <col min="2" max="4" width="19" style="5" customWidth="1"/>
+    <col min="5" max="6" width="30" style="6" customWidth="1"/>
+    <col min="7" max="9" width="39.1640625" style="5" customWidth="1"/>
+    <col min="10" max="12" width="23.5" style="5" customWidth="1"/>
+    <col min="13" max="13" width="36" style="5" customWidth="1"/>
     <col min="14" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -829,563 +772,557 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9">
+        <v>50000000</v>
+      </c>
+      <c r="F2" s="9">
+        <v>1000000000</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6">
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="12">
+        <v>100000000</v>
+      </c>
+      <c r="F3" s="12">
+        <v>1000000000</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9">
+        <v>1000000000</v>
+      </c>
+      <c r="F4" s="9">
+        <v>10000000000</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="12">
+        <v>500000000</v>
+      </c>
+      <c r="F5" s="12">
+        <v>5000000000</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="9">
+        <v>10000000</v>
+      </c>
+      <c r="F6" s="9">
+        <v>100000000</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="F7" s="12">
         <v>50000000</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9">
+        <v>50000000</v>
+      </c>
+      <c r="F8" s="9">
+        <v>500000000</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="12">
         <v>1000000000</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F9" s="12">
+        <v>500000000000</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5" t="s">
+      <c r="K9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+    </row>
+    <row r="10" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="F10" s="9">
+        <v>50000000</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="F11" s="12">
+        <v>100000000</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="F12" s="9">
+        <v>10000000</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="12">
+        <v>10000000</v>
+      </c>
+      <c r="F13" s="12">
+        <v>100000000</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="F14" s="9">
+        <v>25000000</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10">
-        <v>100000000</v>
-      </c>
-      <c r="F3" s="10">
-        <v>1000000000</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="9">
+        <v>5000000</v>
+      </c>
+      <c r="F16" s="9">
+        <v>25000000</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-    </row>
-    <row r="4" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="K16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="11">
-        <v>1000000000</v>
-      </c>
-      <c r="F4" s="11">
-        <v>10000000000</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="13">
-        <v>500000000</v>
-      </c>
-      <c r="F5" s="13">
-        <v>5000000000</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-    </row>
-    <row r="6" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="6">
-        <v>10000000</v>
-      </c>
-      <c r="F6" s="6">
-        <v>100000000</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-    </row>
-    <row r="7" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10">
-        <v>10000000</v>
-      </c>
-      <c r="F7" s="10">
-        <v>50000000</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-    </row>
-    <row r="8" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6">
-        <v>50000000</v>
-      </c>
-      <c r="F8" s="6">
-        <v>500000000</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-    </row>
-    <row r="9" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10">
-        <v>1000000000</v>
-      </c>
-      <c r="F9" s="10">
-        <v>500000000000</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-    </row>
-    <row r="10" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="11">
-        <v>1000000</v>
-      </c>
-      <c r="F10" s="11">
-        <v>50000000</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-    </row>
-    <row r="11" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10">
-        <v>10000000</v>
-      </c>
-      <c r="F11" s="10">
-        <v>100000000</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-    </row>
-    <row r="12" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="11">
-        <v>1000000</v>
-      </c>
-      <c r="F12" s="11">
-        <v>10000000</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-    </row>
-    <row r="13" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="13">
-        <v>10000000</v>
-      </c>
-      <c r="F13" s="13">
-        <v>100000000</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6">
-        <v>1000000</v>
-      </c>
-      <c r="F14" s="6">
-        <v>25000000</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-    </row>
-    <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-    </row>
-    <row r="16" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6">
-        <v>5000000</v>
-      </c>
-      <c r="F16" s="6">
-        <v>25000000</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
     </row>
     <row r="17" ht="35" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>

--- a/data/Internal_Investments_Dashboard.xlsx
+++ b/data/Internal_Investments_Dashboard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/market-dashboard/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/internal-models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AA4812-AE04-5A4B-96BC-DD8676E64D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F212B6ED-62DC-CD46-993B-410DDA69539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6560" yWindow="2480" windowWidth="27640" windowHeight="16680" xr2:uid="{FBFB69EE-18FE-594B-9D4F-6699E2689A0B}"/>
+    <workbookView xWindow="3460" yWindow="2660" windowWidth="27640" windowHeight="16680" xr2:uid="{FBFB69EE-18FE-594B-9D4F-6699E2689A0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments Map Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
   <si>
     <t>Partner</t>
   </si>
@@ -92,6 +92,9 @@
     <t>South-East Asia</t>
   </si>
   <si>
+    <t>India</t>
+  </si>
+  <si>
     <t>Private Equity</t>
   </si>
   <si>
@@ -110,12 +113,18 @@
     <t>Europe</t>
   </si>
   <si>
+    <t xml:space="preserve"> Later-Stage</t>
+  </si>
+  <si>
     <t>Broad</t>
   </si>
   <si>
     <t>Apollo Private Equity</t>
   </si>
   <si>
+    <t>Asia-Pacific</t>
+  </si>
+  <si>
     <t>Lone Star</t>
   </si>
   <si>
@@ -143,6 +152,12 @@
     <t>Tiger Global Private Investment Partners</t>
   </si>
   <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Growth</t>
+  </si>
+  <si>
     <t>Tiger Global Crossover</t>
   </si>
   <si>
@@ -152,6 +167,9 @@
     <t>Seed</t>
   </si>
   <si>
+    <t xml:space="preserve"> Early-Stage</t>
+  </si>
+  <si>
     <t>Intellectual Property</t>
   </si>
   <si>
@@ -170,6 +188,9 @@
     <t>B2B SaaS</t>
   </si>
   <si>
+    <t xml:space="preserve"> fintech</t>
+  </si>
+  <si>
     <t>Incus Capital</t>
   </si>
   <si>
@@ -179,6 +200,15 @@
     <t>Renewables</t>
   </si>
   <si>
+    <t xml:space="preserve"> Energy transition</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> essential services</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> public transport</t>
+  </si>
+  <si>
     <t>Grovepoint</t>
   </si>
   <si>
@@ -194,25 +224,7 @@
     <t xml:space="preserve">Private Equity </t>
   </si>
   <si>
-    <t>South Asia</t>
-  </si>
-  <si>
-    <t>Later-Stage</t>
-  </si>
-  <si>
-    <t>East Asia</t>
-  </si>
-  <si>
-    <t>Fintech</t>
-  </si>
-  <si>
-    <t>Energy transition</t>
-  </si>
-  <si>
-    <t>Essential services</t>
-  </si>
-  <si>
-    <t>Public transport</t>
+    <t xml:space="preserve"> Mature</t>
   </si>
 </sst>
 </file>
@@ -221,9 +233,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -247,10 +259,21 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -269,12 +292,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -325,16 +348,31 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="7"/>
+        <color rgb="FF4472C4"/>
       </left>
       <right style="thin">
-        <color theme="7"/>
+        <color rgb="FFB4C6E7"/>
       </right>
       <top style="thin">
-        <color theme="7"/>
+        <color rgb="FFB4C6E7"/>
       </top>
       <bottom style="thin">
-        <color theme="7"/>
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -343,7 +381,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -354,27 +392,46 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -714,11 +771,11 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="4" width="19" style="5" customWidth="1"/>
-    <col min="5" max="6" width="30" style="6" customWidth="1"/>
-    <col min="7" max="9" width="39.1640625" style="5" customWidth="1"/>
-    <col min="10" max="12" width="23.5" style="5" customWidth="1"/>
-    <col min="13" max="13" width="36" style="5" customWidth="1"/>
+    <col min="2" max="4" width="19" style="16" customWidth="1"/>
+    <col min="5" max="6" width="30" style="17" customWidth="1"/>
+    <col min="7" max="9" width="39.1640625" style="16" customWidth="1"/>
+    <col min="10" max="12" width="23.5" style="16" customWidth="1"/>
+    <col min="13" max="13" width="36" style="16" customWidth="1"/>
     <col min="14" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -772,557 +829,563 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6">
+        <v>50000000</v>
+      </c>
+      <c r="F2" s="6">
+        <v>1000000000</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+    </row>
+    <row r="3" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="F3" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+    </row>
+    <row r="4" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="11">
+        <v>1000000000</v>
+      </c>
+      <c r="F4" s="11">
+        <v>10000000000</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+    </row>
+    <row r="5" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="13">
+        <v>500000000</v>
+      </c>
+      <c r="F5" s="13">
+        <v>5000000000</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+    </row>
+    <row r="6" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="6">
+        <v>10000000</v>
+      </c>
+      <c r="F6" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="10">
+        <v>10000000</v>
+      </c>
+      <c r="F7" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+    </row>
+    <row r="8" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6">
+        <v>50000000</v>
+      </c>
+      <c r="F8" s="6">
+        <v>500000000</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+    </row>
+    <row r="9" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="F9" s="10">
+        <v>500000000000</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+    </row>
+    <row r="10" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="F10" s="11">
+        <v>50000000</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+    </row>
+    <row r="11" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="10">
+        <v>10000000</v>
+      </c>
+      <c r="F11" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+    </row>
+    <row r="12" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="F12" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+    </row>
+    <row r="13" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="13">
+        <v>10000000</v>
+      </c>
+      <c r="F13" s="13">
+        <v>100000000</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9">
-        <v>50000000</v>
-      </c>
-      <c r="F2" s="9">
-        <v>1000000000</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8" t="s">
+      <c r="I13" s="14"/>
+      <c r="J13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="F14" s="6">
+        <v>25000000</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8" t="s">
+      <c r="H14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+    </row>
+    <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+    </row>
+    <row r="16" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6">
+        <v>5000000</v>
+      </c>
+      <c r="F16" s="6">
+        <v>25000000</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12">
-        <v>100000000</v>
-      </c>
-      <c r="F3" s="12">
-        <v>1000000000</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9">
-        <v>1000000000</v>
-      </c>
-      <c r="F4" s="9">
-        <v>10000000000</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="K16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="12">
-        <v>500000000</v>
-      </c>
-      <c r="F5" s="12">
-        <v>5000000000</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="9">
-        <v>10000000</v>
-      </c>
-      <c r="F6" s="9">
-        <v>100000000</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12">
-        <v>10000000</v>
-      </c>
-      <c r="F7" s="12">
-        <v>50000000</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9">
-        <v>50000000</v>
-      </c>
-      <c r="F8" s="9">
-        <v>500000000</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12">
-        <v>1000000000</v>
-      </c>
-      <c r="F9" s="12">
-        <v>500000000000</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9">
-        <v>1000000</v>
-      </c>
-      <c r="F10" s="9">
-        <v>50000000</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12">
-        <v>10000000</v>
-      </c>
-      <c r="F11" s="12">
-        <v>100000000</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9">
-        <v>1000000</v>
-      </c>
-      <c r="F12" s="9">
-        <v>10000000</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="12">
-        <v>10000000</v>
-      </c>
-      <c r="F13" s="12">
-        <v>100000000</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="P13" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9">
-        <v>1000000</v>
-      </c>
-      <c r="F14" s="9">
-        <v>25000000</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="9">
-        <v>5000000</v>
-      </c>
-      <c r="F16" s="9">
-        <v>25000000</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8" t="s">
-        <v>40</v>
-      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
     </row>
     <row r="17" ht="35" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>

--- a/data/Internal_Investments_Dashboard.xlsx
+++ b/data/Internal_Investments_Dashboard.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/internal-models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F212B6ED-62DC-CD46-993B-410DDA69539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BEB4E1A-C7A7-8049-B99D-053C00339DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3460" yWindow="2660" windowWidth="27640" windowHeight="16680" xr2:uid="{FBFB69EE-18FE-594B-9D4F-6699E2689A0B}"/>
+    <workbookView xWindow="3480" yWindow="2660" windowWidth="27640" windowHeight="16680" xr2:uid="{4930D9E8-EC32-2740-B70C-4A799C618033}"/>
   </bookViews>
   <sheets>
-    <sheet name="Investments Map Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Master Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="59">
   <si>
     <t>Partner</t>
   </si>
@@ -71,28 +71,28 @@
     <t>Stage of Investment 1</t>
   </si>
   <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Sector 1</t>
+  </si>
+  <si>
+    <t>Sector 2</t>
+  </si>
+  <si>
+    <t>Sector 3</t>
+  </si>
+  <si>
     <t>Invested</t>
   </si>
   <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Sector 1</t>
-  </si>
-  <si>
-    <t>Sector 2</t>
-  </si>
-  <si>
-    <t>Sector 3</t>
-  </si>
-  <si>
     <t>Asia Partners</t>
   </si>
   <si>
     <t>South-East Asia</t>
   </si>
   <si>
-    <t>India</t>
+    <t>South Asia</t>
   </si>
   <si>
     <t>Private Equity</t>
@@ -113,7 +113,7 @@
     <t>Europe</t>
   </si>
   <si>
-    <t xml:space="preserve"> Later-Stage</t>
+    <t>Later-Stage</t>
   </si>
   <si>
     <t>Broad</t>
@@ -122,12 +122,15 @@
     <t>Apollo Private Equity</t>
   </si>
   <si>
-    <t>Asia-Pacific</t>
+    <t>Global with exclusions</t>
   </si>
   <si>
     <t>Lone Star</t>
   </si>
   <si>
+    <t>East Asia</t>
+  </si>
+  <si>
     <t>Stonehage Fleming Private Investments</t>
   </si>
   <si>
@@ -143,21 +146,12 @@
     <t>Bietou Capital</t>
   </si>
   <si>
-    <t>Global with exclusions</t>
-  </si>
-  <si>
     <t>Mature</t>
   </si>
   <si>
     <t>Tiger Global Private Investment Partners</t>
   </si>
   <si>
-    <t>Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Growth</t>
-  </si>
-  <si>
     <t>Tiger Global Crossover</t>
   </si>
   <si>
@@ -167,28 +161,25 @@
     <t>Seed</t>
   </si>
   <si>
-    <t xml:space="preserve"> Early-Stage</t>
-  </si>
-  <si>
     <t>Intellectual Property</t>
   </si>
   <si>
     <t>Jordan Partners</t>
   </si>
   <si>
+    <t>B2B</t>
+  </si>
+  <si>
     <t>Not Invested</t>
   </si>
   <si>
-    <t>B2B</t>
-  </si>
-  <si>
     <t>Defiant</t>
   </si>
   <si>
     <t>B2B SaaS</t>
   </si>
   <si>
-    <t xml:space="preserve"> fintech</t>
+    <t>Fintech</t>
   </si>
   <si>
     <t>Incus Capital</t>
@@ -200,13 +191,13 @@
     <t>Renewables</t>
   </si>
   <si>
-    <t xml:space="preserve"> Energy transition</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> essential services</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> public transport</t>
+    <t>Energy transition</t>
+  </si>
+  <si>
+    <t>Essential services</t>
+  </si>
+  <si>
+    <t>Public transport</t>
   </si>
   <si>
     <t>Grovepoint</t>
@@ -222,9 +213,6 @@
   </si>
   <si>
     <t xml:space="preserve">Private Equity </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mature</t>
   </si>
 </sst>
 </file>
@@ -233,9 +221,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -252,28 +240,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -286,18 +264,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor theme="7" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -307,72 +285,77 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF4472C4"/>
+        <color theme="7"/>
       </left>
       <right style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </right>
       <top style="thin">
-        <color rgb="FF4472C4"/>
+        <color theme="7"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB4C6E7"/>
-      </right>
+      <right/>
       <top style="thin">
-        <color rgb="FF4472C4"/>
+        <color theme="7"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB4C6E7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB4C6E7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB4C6E7"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF4472C4"/>
+        <color theme="7"/>
       </left>
       <right style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </right>
       <top style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB4C6E7"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="7"/>
       </left>
       <right style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </right>
+      <top style="medium">
+        <color theme="7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="7"/>
+      </left>
+      <right/>
       <top style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB4C6E7"/>
+        <color theme="7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -381,57 +364,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -766,21 +750,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD116F1-5EB1-BC40-9EB8-BFB75BCF5702}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED836A7C-E39B-F941-BC19-962B581A0C12}">
   <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="4" width="19" style="16" customWidth="1"/>
-    <col min="5" max="6" width="30" style="17" customWidth="1"/>
-    <col min="7" max="9" width="39.1640625" style="16" customWidth="1"/>
-    <col min="10" max="12" width="23.5" style="16" customWidth="1"/>
-    <col min="13" max="13" width="36" style="16" customWidth="1"/>
-    <col min="14" max="16" width="30" customWidth="1"/>
+    <col min="1" max="4" width="38" style="1" customWidth="1"/>
+    <col min="5" max="6" width="30" customWidth="1"/>
+    <col min="7" max="9" width="39.1640625" style="1" customWidth="1"/>
+    <col min="10" max="11" width="23.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="36" style="1" customWidth="1"/>
+    <col min="13" max="15" width="30" style="1" customWidth="1"/>
+    <col min="16" max="16" width="23.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:16" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -792,10 +776,10 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -813,7 +797,7 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
@@ -825,570 +809,565 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6">
+      <c r="D2" s="6"/>
+      <c r="E2" s="7">
         <v>50000000</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="7">
         <v>1000000000</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5" t="s">
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="5" t="s">
+      <c r="K2" s="6"/>
+      <c r="L2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10">
+      <c r="D3" s="10"/>
+      <c r="E3" s="11">
         <v>100000000</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="11">
         <v>1000000000</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="9" t="s">
+      <c r="L3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-    </row>
-    <row r="4" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="15">
+        <v>1000000000</v>
+      </c>
+      <c r="F4" s="15">
+        <v>10000000000</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="11">
+        <v>500000000</v>
+      </c>
+      <c r="F5" s="11">
+        <v>5000000000</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="15">
+        <v>10000000</v>
+      </c>
+      <c r="F6" s="15">
+        <v>100000000</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="11">
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="F7" s="11">
+        <v>50000000</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15">
+        <v>50000000</v>
+      </c>
+      <c r="F8" s="15">
+        <v>500000000</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11">
         <v>1000000000</v>
       </c>
-      <c r="F4" s="11">
-        <v>10000000000</v>
-      </c>
-      <c r="G4" s="12" t="s">
+      <c r="F9" s="11">
+        <v>500000000000</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="5" t="s">
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="5" t="s">
+      <c r="L9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="15">
+        <v>1000000</v>
+      </c>
+      <c r="F10" s="15">
+        <v>50000000</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="F11" s="11">
+        <v>100000000</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15">
+        <v>1000000</v>
+      </c>
+      <c r="F12" s="15">
+        <v>10000000</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="F13" s="11">
+        <v>100000000</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14" s="15">
+        <v>1000000</v>
+      </c>
+      <c r="F14" s="15">
+        <v>25000000</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="13">
-        <v>500000000</v>
-      </c>
-      <c r="F5" s="13">
-        <v>5000000000</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="9" t="s">
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="19">
+        <v>5000000</v>
+      </c>
+      <c r="F16" s="19">
+        <v>25000000</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="9" t="s">
+      <c r="K16" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-    </row>
-    <row r="6" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="6">
-        <v>10000000</v>
-      </c>
-      <c r="F6" s="6">
-        <v>100000000</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-    </row>
-    <row r="7" spans="1:16" s="7" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10">
-        <v>10000000</v>
-      </c>
-      <c r="F7" s="10">
-        <v>50000000</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-    </row>
-    <row r="8" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6">
-        <v>50000000</v>
-      </c>
-      <c r="F8" s="6">
-        <v>500000000</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-    </row>
-    <row r="9" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10">
-        <v>1000000000</v>
-      </c>
-      <c r="F9" s="10">
-        <v>500000000000</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-    </row>
-    <row r="10" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="11">
-        <v>1000000</v>
-      </c>
-      <c r="F10" s="11">
-        <v>50000000</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="5" t="s">
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-    </row>
-    <row r="11" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10">
-        <v>10000000</v>
-      </c>
-      <c r="F11" s="10">
-        <v>100000000</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-    </row>
-    <row r="12" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="11">
-        <v>1000000</v>
-      </c>
-      <c r="F12" s="11">
-        <v>10000000</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-    </row>
-    <row r="13" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="13">
-        <v>10000000</v>
-      </c>
-      <c r="F13" s="13">
-        <v>100000000</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6">
-        <v>1000000</v>
-      </c>
-      <c r="F14" s="6">
-        <v>25000000</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-    </row>
-    <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-    </row>
-    <row r="16" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6">
-        <v>5000000</v>
-      </c>
-      <c r="F16" s="6">
-        <v>25000000</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
     </row>
     <row r="17" ht="35" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/Internal_Investments_Dashboard.xlsx
+++ b/data/Internal_Investments_Dashboard.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/market-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BEB4E1A-C7A7-8049-B99D-053C00339DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F174F1B3-D78C-C947-BD89-C7A72954B105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3480" yWindow="2660" windowWidth="27640" windowHeight="16680" xr2:uid="{4930D9E8-EC32-2740-B70C-4A799C618033}"/>
   </bookViews>
   <sheets>
-    <sheet name="Master Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Investments Map Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -379,41 +379,41 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>

--- a/data/Internal_Investments_Dashboard.xlsx
+++ b/data/Internal_Investments_Dashboard.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/market-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F174F1B3-D78C-C947-BD89-C7A72954B105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABCDABF-B657-854F-A253-B4EEC147B11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="2660" windowWidth="27640" windowHeight="16680" xr2:uid="{4930D9E8-EC32-2740-B70C-4A799C618033}"/>
+    <workbookView xWindow="3440" yWindow="2640" windowWidth="27640" windowHeight="16680" xr2:uid="{4930D9E8-EC32-2740-B70C-4A799C618033}"/>
   </bookViews>
   <sheets>
-    <sheet name="Investments Map Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Master Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>

--- a/data/Internal_Investments_Dashboard.xlsx
+++ b/data/Internal_Investments_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mornay/Documents/market-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABCDABF-B657-854F-A253-B4EEC147B11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E584B2A1-CC88-8548-81F2-D1838F096C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3440" yWindow="2640" windowWidth="27640" windowHeight="16680" xr2:uid="{4930D9E8-EC32-2740-B70C-4A799C618033}"/>
   </bookViews>
@@ -1302,7 +1302,7 @@
       <c r="N14" s="14"/>
       <c r="O14" s="14"/>
       <c r="P14" s="16" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="35" customHeight="1" x14ac:dyDescent="0.2">
